--- a/MBSE D2DC/System_Requirements_Register.xlsx
+++ b/MBSE D2DC/System_Requirements_Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karukkuvel\OneDrive\Documents\MBSE\MBSE-D2DC-Challenge\MBSE D2DC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69FED02-BD86-4394-A256-30FBEB29226F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D08871-A6D1-4147-8EBA-A9402BDA1ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
